--- a/data/screening_agreement/reviewer_agreement_rayyan.xlsx
+++ b/data/screening_agreement/reviewer_agreement_rayyan.xlsx
@@ -5,27 +5,42 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\work\Projects\In_progress\conservation_evidence_factors_synthesis\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\work\Projects\In_progress\conservation_evidence_factors_synthesis\data\screening_agreement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2329FAD-381E-44E4-81E3-8C4F6A076784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C02A59-019C-4F25-855C-819CAA3118C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BAEAB964-30E6-45DA-AD2A-F46573CA4E4F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BAEAB964-30E6-45DA-AD2A-F46573CA4E4F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="abstracts" sheetId="1" r:id="rId1"/>
+    <sheet name="full text" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
   <si>
     <t>Reviewer name</t>
   </si>
@@ -178,6 +193,51 @@
   </si>
   <si>
     <t>Meet to discuss disagreements</t>
+  </si>
+  <si>
+    <t>Both included</t>
+  </si>
+  <si>
+    <t>Both excluded</t>
+  </si>
+  <si>
+    <t>Only Phil included</t>
+  </si>
+  <si>
+    <t>Only user included</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Cohen's kappa</t>
+  </si>
+  <si>
+    <t>po</t>
+  </si>
+  <si>
+    <t>pe</t>
+  </si>
+  <si>
+    <t>p(yes)</t>
+  </si>
+  <si>
+    <t>p(No)</t>
+  </si>
+  <si>
+    <t>Aiden</t>
+  </si>
+  <si>
+    <t>Round</t>
+  </si>
+  <si>
+    <t>Round 1</t>
+  </si>
+  <si>
+    <t>Round 2</t>
+  </si>
+  <si>
+    <t>Round 3</t>
   </si>
 </sst>
 </file>
@@ -844,6 +904,12 @@
       <c r="E13">
         <v>121</v>
       </c>
+      <c r="F13">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="G13">
+        <v>134</v>
+      </c>
       <c r="H13" t="s">
         <v>49</v>
       </c>
@@ -1132,4 +1198,973 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD753D87-F8AB-4555-8F8D-B54A1CCDF3DC}">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <f>(B2+C2)/SUM(B2:E2)</f>
+        <v>0.9</v>
+      </c>
+      <c r="G2">
+        <f>((B2+D2)/SUM(B2:E2))*((B2+E2)/SUM(B2:E2))</f>
+        <v>0.42</v>
+      </c>
+      <c r="H2">
+        <f>((C2+E2)/SUM(B2:E2))*((C2+D2)/SUM(B2:E2))</f>
+        <v>0.12</v>
+      </c>
+      <c r="I2">
+        <f>G2+H2</f>
+        <v>0.54</v>
+      </c>
+      <c r="J2">
+        <f>(F2-I2)/(1-I2)</f>
+        <v>0.78260869565217395</v>
+      </c>
+      <c r="K2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F7" si="0">(B3+C3)/SUM(B3:E3)</f>
+        <v>0.9</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G7" si="1">((B3+D3)/SUM(B3:E3))*((B3+E3)/SUM(B3:E3))</f>
+        <v>0.3</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H7" si="2">((C3+E3)/SUM(B3:E3))*((C3+D3)/SUM(B3:E3))</f>
+        <v>0.2</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I7" si="3">G3+H3</f>
+        <v>0.5</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J7" si="4">(F3-I3)/(1-I3)</f>
+        <v>0.8</v>
+      </c>
+      <c r="K3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="4"/>
+        <v>-0.66666666666666674</v>
+      </c>
+      <c r="K4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>0.6</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="4"/>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="K6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="K7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <f t="shared" ref="F8:F15" si="5">(B8+C8)/SUM(B8:E8)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G8">
+        <f t="shared" ref="G8:G15" si="6">((B8+D8)/SUM(B8:E8))*((B8+E8)/SUM(B8:E8))</f>
+        <v>0.48</v>
+      </c>
+      <c r="H8">
+        <f t="shared" ref="H8:H15" si="7">((C8+E8)/SUM(B8:E8))*((C8+D8)/SUM(B8:E8))</f>
+        <v>8.0000000000000016E-2</v>
+      </c>
+      <c r="I8">
+        <f t="shared" ref="I8:I15" si="8">G8+H8</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J8">
+        <f t="shared" ref="J8:J15" si="9">(F8-I8)/(1-I8)</f>
+        <v>0.54545454545454553</v>
+      </c>
+      <c r="K8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="6"/>
+        <v>0.42</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="7"/>
+        <v>0.12</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="8"/>
+        <v>0.54</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="9"/>
+        <v>0.34782608695652162</v>
+      </c>
+      <c r="K9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="6"/>
+        <v>0.36</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="7"/>
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="8"/>
+        <v>0.52</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="9"/>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="K10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="6"/>
+        <v>0.3</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="7"/>
+        <v>0.2</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="8"/>
+        <v>0.5</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="9"/>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="K11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="5"/>
+        <v>0.9</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="6"/>
+        <v>0.42</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="7"/>
+        <v>0.12</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="8"/>
+        <v>0.54</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="9"/>
+        <v>0.78260869565217395</v>
+      </c>
+      <c r="K12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="5"/>
+        <v>0.6</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="6"/>
+        <v>0.48999999999999994</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="7"/>
+        <v>0.09</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="8"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="9"/>
+        <v>4.7619047619047658E-2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="5"/>
+        <v>0.9</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="6"/>
+        <v>0.42</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="7"/>
+        <v>0.12</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="8"/>
+        <v>0.54</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="9"/>
+        <v>0.78260869565217395</v>
+      </c>
+      <c r="K14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="5"/>
+        <v>0.9</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="6"/>
+        <v>0.55999999999999994</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="7"/>
+        <v>0.06</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="8"/>
+        <v>0.61999999999999988</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="9"/>
+        <v>0.73684210526315808</v>
+      </c>
+      <c r="K15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <f t="shared" ref="F16" si="10">(B16+C16)/SUM(B16:E16)</f>
+        <v>0.9</v>
+      </c>
+      <c r="G16">
+        <f t="shared" ref="G16" si="11">((B16+D16)/SUM(B16:E16))*((B16+E16)/SUM(B16:E16))</f>
+        <v>0.55999999999999994</v>
+      </c>
+      <c r="H16">
+        <f t="shared" ref="H16" si="12">((C16+E16)/SUM(B16:E16))*((C16+D16)/SUM(B16:E16))</f>
+        <v>0.06</v>
+      </c>
+      <c r="I16">
+        <f t="shared" ref="I16" si="13">G16+H16</f>
+        <v>0.61999999999999988</v>
+      </c>
+      <c r="J16">
+        <f t="shared" ref="J16" si="14">(F16-I16)/(1-I16)</f>
+        <v>0.73684210526315808</v>
+      </c>
+      <c r="K16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <f t="shared" ref="F17:F23" si="15">(B17+C17)/SUM(B17:E17)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G17">
+        <f t="shared" ref="G17:G23" si="16">((B17+D17)/SUM(B17:E17))*((B17+E17)/SUM(B17:E17))</f>
+        <v>0.36</v>
+      </c>
+      <c r="H17">
+        <f t="shared" ref="H17:H23" si="17">((C17+E17)/SUM(B17:E17))*((C17+D17)/SUM(B17:E17))</f>
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="I17">
+        <f t="shared" ref="I17:I23" si="18">G17+H17</f>
+        <v>0.52</v>
+      </c>
+      <c r="J17">
+        <f t="shared" ref="J17:J23" si="19">(F17-I17)/(1-I17)</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="K17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="15"/>
+        <v>0.8</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="16"/>
+        <v>0.36</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="17"/>
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="18"/>
+        <v>0.52</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="19"/>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="K18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="15"/>
+        <v>0.8</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="16"/>
+        <v>0.24</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="17"/>
+        <v>0.24</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="18"/>
+        <v>0.48</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="19"/>
+        <v>0.61538461538461553</v>
+      </c>
+      <c r="K19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="15"/>
+        <v>0.7</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="16"/>
+        <v>0.18</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="17"/>
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="18"/>
+        <v>0.45999999999999996</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="19"/>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="K20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="15"/>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="16"/>
+        <v>7.407407407407407E-2</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="17"/>
+        <v>0.29629629629629628</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="18"/>
+        <v>0.37037037037037035</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="19"/>
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="K21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="15"/>
+        <v>0.9</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="16"/>
+        <v>0.42</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="17"/>
+        <v>0.12</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="18"/>
+        <v>0.54</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="19"/>
+        <v>0.78260869565217395</v>
+      </c>
+      <c r="K22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="15"/>
+        <v>0.2</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="16"/>
+        <v>0.24</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="17"/>
+        <v>0.24</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="18"/>
+        <v>0.48</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="19"/>
+        <v>-0.53846153846153844</v>
+      </c>
+      <c r="K23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <f t="shared" ref="F24" si="20">(B24+C24)/SUM(B24:E24)</f>
+        <v>0.9</v>
+      </c>
+      <c r="G24">
+        <f t="shared" ref="G24" si="21">((B24+D24)/SUM(B24:E24))*((B24+E24)/SUM(B24:E24))</f>
+        <v>0.3</v>
+      </c>
+      <c r="H24">
+        <f t="shared" ref="H24" si="22">((C24+E24)/SUM(B24:E24))*((C24+D24)/SUM(B24:E24))</f>
+        <v>0.2</v>
+      </c>
+      <c r="I24">
+        <f t="shared" ref="I24" si="23">G24+H24</f>
+        <v>0.5</v>
+      </c>
+      <c r="J24">
+        <f t="shared" ref="J24" si="24">(F24-I24)/(1-I24)</f>
+        <v>0.8</v>
+      </c>
+      <c r="K24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/screening_agreement/reviewer_agreement_rayyan.xlsx
+++ b/data/screening_agreement/reviewer_agreement_rayyan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\work\Projects\In_progress\conservation_evidence_factors_synthesis\data\screening_agreement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C02A59-019C-4F25-855C-819CAA3118C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DDA04C-2DC7-483C-BA3C-3BC629EEF2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BAEAB964-30E6-45DA-AD2A-F46573CA4E4F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{BAEAB964-30E6-45DA-AD2A-F46573CA4E4F}"/>
   </bookViews>
   <sheets>
     <sheet name="abstracts" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="67">
   <si>
     <t>Reviewer name</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Round 3</t>
+  </si>
+  <si>
+    <t>mean overall</t>
   </si>
 </sst>
 </file>
@@ -590,20 +593,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{127713FE-D749-46EE-B0DE-3497415C3136}">
   <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.81640625" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" customWidth="1"/>
     <col min="8" max="8" width="32" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -635,7 +638,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -655,7 +658,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -675,7 +678,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -701,7 +704,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -727,7 +730,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -747,7 +750,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -767,7 +770,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -793,7 +796,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -810,7 +813,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -836,7 +839,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -856,7 +859,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -888,7 +891,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -920,7 +923,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -946,7 +949,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -966,7 +969,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -992,7 +995,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1018,7 +1021,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1044,7 +1047,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1064,7 +1067,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -1084,7 +1087,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -1116,7 +1119,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -1142,7 +1145,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1168,7 +1171,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1202,17 +1205,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD753D87-F8AB-4555-8F8D-B54A1CCDF3DC}">
-  <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.26953125" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -1246,8 +1249,11 @@
       <c r="K1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1286,8 +1292,12 @@
       <c r="K2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M2">
+        <f>AVERAGE(J2,J3,J7,J12,J14,J15,J16,J17,J18,J19,J20,J22,J24)</f>
+        <v>0.71004728612544155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1327,7 +1337,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1367,7 +1377,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1407,7 +1417,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1447,7 +1457,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1487,7 +1497,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -1527,7 +1537,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1567,7 +1577,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1607,7 +1617,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1647,7 +1657,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1687,7 +1697,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1727,7 +1737,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1767,7 +1777,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1807,7 +1817,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1847,7 +1857,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -1887,7 +1897,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1927,7 +1937,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1967,7 +1977,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2007,7 +2017,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -2047,7 +2057,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -2087,7 +2097,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -2127,7 +2137,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
